--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$93</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3266" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="630">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -214,13 +214,209 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Observation.implicitRules</t>
+    <t>Observation.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Observation.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Observation.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>Observation.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Observation.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Observation.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -231,9 +427,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>Observation.language</t>
@@ -316,38 +509,10 @@
     <t>Observation.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Observation.extension:bodyposition</t>
@@ -580,39 +745,16 @@
     <t>Observation.category.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Observation.category:VSCat.extension</t>
   </si>
   <si>
     <t>Observation.category.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Observation.category:VSCat.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -833,9 +975,6 @@
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
@@ -1061,10 +1200,6 @@
     <t>Observation.issued</t>
   </si>
   <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
     <t>Date/Time this version was made available</t>
   </si>
   <si>
@@ -1420,9 +1555,6 @@
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -2169,7 +2301,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP84"/>
+  <dimension ref="A1:AP93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.453125" customWidth="true" bestFit="true"/>
@@ -2195,7 +2327,7 @@
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="88.15234375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="85.10546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="21.17578125" customWidth="true" bestFit="true"/>
@@ -2594,10 +2726,10 @@
         <v>37</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>64</v>
@@ -2608,9 +2740,7 @@
       <c r="M4" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="N4" t="s" s="2">
-        <v>67</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>37</v>
@@ -2659,7 +2789,7 @@
         <v>37</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>35</v>
@@ -2668,10 +2798,10 @@
         <v>48</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>37</v>
@@ -2683,7 +2813,7 @@
         <v>37</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>37</v>
@@ -2694,21 +2824,21 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>37</v>
@@ -2755,28 +2885,28 @@
         <v>37</v>
       </c>
       <c r="X5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB5" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Y5" t="s" s="2">
+      <c r="AC5" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Z5" t="s" s="2">
+      <c r="AD5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE5" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>37</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>78</v>
@@ -2785,13 +2915,13 @@
         <v>35</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>37</v>
@@ -2803,7 +2933,7 @@
         <v>37</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>37</v>
@@ -2814,14 +2944,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2837,19 +2967,19 @@
         <v>37</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2899,7 +3029,7 @@
         <v>37</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>35</v>
@@ -2923,7 +3053,7 @@
         <v>37</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>37</v>
@@ -2934,21 +3064,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>37</v>
@@ -2957,19 +3087,19 @@
         <v>37</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3019,19 +3149,19 @@
         <v>37</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>37</v>
@@ -3043,7 +3173,7 @@
         <v>37</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>37</v>
@@ -3054,21 +3184,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>37</v>
@@ -3077,19 +3207,19 @@
         <v>37</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3127,31 +3257,31 @@
         <v>37</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>37</v>
@@ -3163,7 +3293,7 @@
         <v>37</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>37</v>
@@ -3174,14 +3304,12 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>37</v>
       </c>
@@ -3190,7 +3318,7 @@
         <v>35</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>37</v>
@@ -3199,18 +3327,20 @@
         <v>37</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>37</v>
@@ -3247,19 +3377,19 @@
         <v>37</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>35</v>
@@ -3271,7 +3401,7 @@
         <v>60</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>37</v>
@@ -3283,7 +3413,7 @@
         <v>37</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>37</v>
@@ -3294,13 +3424,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>37</v>
@@ -3313,24 +3443,26 @@
         <v>48</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>37</v>
@@ -3340,7 +3472,7 @@
         <v>37</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>37</v>
@@ -3379,7 +3511,7 @@
         <v>37</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>35</v>
@@ -3391,7 +3523,7 @@
         <v>60</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>37</v>
@@ -3403,7 +3535,7 @@
         <v>37</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>37</v>
@@ -3414,14 +3546,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3434,26 +3566,24 @@
         <v>37</v>
       </c>
       <c r="I11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="J11" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>37</v>
       </c>
@@ -3477,31 +3607,31 @@
         <v>37</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>35</v>
@@ -3513,7 +3643,7 @@
         <v>60</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>37</v>
@@ -3522,10 +3652,10 @@
         <v>37</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>37</v>
@@ -3536,10 +3666,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3562,18 +3692,18 @@
         <v>49</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>124</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>37</v>
       </c>
@@ -3597,13 +3727,13 @@
         <v>37</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>37</v>
@@ -3621,7 +3751,7 @@
         <v>37</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>35</v>
@@ -3636,19 +3766,19 @@
         <v>61</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>128</v>
+        <v>37</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>37</v>
@@ -3656,46 +3786,44 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>49</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>37</v>
       </c>
@@ -3743,31 +3871,31 @@
         <v>37</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>37</v>
@@ -3778,21 +3906,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>37</v>
@@ -3801,19 +3929,19 @@
         <v>37</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3839,13 +3967,13 @@
         <v>37</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>37</v>
@@ -3863,31 +3991,31 @@
         <v>37</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>147</v>
+        <v>37</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>148</v>
+        <v>68</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>37</v>
@@ -3898,46 +4026,44 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>48</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>37</v>
       </c>
@@ -3961,13 +4087,13 @@
         <v>37</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>156</v>
+        <v>37</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>37</v>
@@ -3985,10 +4111,10 @@
         <v>37</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>48</v>
@@ -4000,19 +4126,19 @@
         <v>61</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>158</v>
+        <v>37</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>159</v>
+        <v>37</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>161</v>
+        <v>37</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>37</v>
@@ -4020,24 +4146,24 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>37</v>
@@ -4046,20 +4172,18 @@
         <v>37</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>37</v>
       </c>
@@ -4083,29 +4207,31 @@
         <v>37</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AC16" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="AD16" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>35</v>
@@ -4114,10 +4240,10 @@
         <v>36</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>37</v>
@@ -4126,13 +4252,13 @@
         <v>37</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>172</v>
+        <v>62</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>173</v>
+        <v>37</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>37</v>
@@ -4140,26 +4266,24 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>37</v>
@@ -4168,20 +4292,18 @@
         <v>37</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>37</v>
       </c>
@@ -4205,31 +4327,31 @@
         <v>37</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB17" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Y17" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="AC17" t="s" s="2">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>35</v>
@@ -4241,7 +4363,7 @@
         <v>60</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>37</v>
@@ -4250,13 +4372,13 @@
         <v>37</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>172</v>
+        <v>62</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>173</v>
+        <v>37</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>37</v>
@@ -4264,12 +4386,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>37</v>
       </c>
@@ -4290,13 +4414,13 @@
         <v>37</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4347,19 +4471,19 @@
         <v>37</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>37</v>
@@ -4371,7 +4495,7 @@
         <v>37</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>37</v>
@@ -4382,24 +4506,26 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>37</v>
@@ -4408,17 +4534,15 @@
         <v>37</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>99</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>37</v>
@@ -4455,19 +4579,19 @@
         <v>37</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>35</v>
@@ -4479,7 +4603,7 @@
         <v>60</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>37</v>
@@ -4502,45 +4626,45 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="J20" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>191</v>
+        <v>74</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>37</v>
@@ -4577,19 +4701,19 @@
         <v>37</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>35</v>
@@ -4601,7 +4725,7 @@
         <v>60</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>37</v>
@@ -4610,10 +4734,10 @@
         <v>37</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>194</v>
+        <v>37</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>195</v>
+        <v>62</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>37</v>
@@ -4624,10 +4748,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4638,7 +4762,7 @@
         <v>35</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>37</v>
@@ -4647,19 +4771,21 @@
         <v>37</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>37</v>
       </c>
@@ -4707,34 +4833,34 @@
         <v>37</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>37</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>37</v>
@@ -4742,14 +4868,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4765,21 +4891,23 @@
         <v>37</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>37</v>
       </c>
@@ -4815,19 +4943,19 @@
         <v>37</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>35</v>
@@ -4839,19 +4967,19 @@
         <v>60</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>37</v>
+        <v>190</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>37</v>
+        <v>191</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>62</v>
+        <v>192</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>37</v>
@@ -4862,24 +4990,24 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>37</v>
+        <v>194</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>37</v>
@@ -4888,26 +5016,24 @@
         <v>49</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>64</v>
+        <v>195</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>206</v>
+        <v>37</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>37</v>
@@ -4949,31 +5075,31 @@
         <v>37</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>37</v>
+        <v>199</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>37</v>
@@ -4984,10 +5110,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4995,33 +5121,35 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>48</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>49</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>37</v>
       </c>
@@ -5045,13 +5173,13 @@
         <v>37</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>37</v>
+        <v>208</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>37</v>
+        <v>209</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>37</v>
@@ -5069,10 +5197,10 @@
         <v>37</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>48</v>
@@ -5084,19 +5212,19 @@
         <v>61</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>37</v>
+        <v>210</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>37</v>
+        <v>211</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>37</v>
+        <v>214</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>37</v>
@@ -5104,10 +5232,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5118,7 +5246,7 @@
         <v>48</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>49</v>
@@ -5127,29 +5255,29 @@
         <v>37</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>71</v>
+        <v>216</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>224</v>
+        <v>37</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>37</v>
@@ -5167,37 +5295,35 @@
         <v>37</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>37</v>
+        <v>221</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>37</v>
+        <v>222</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>37</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>60</v>
@@ -5212,13 +5338,13 @@
         <v>37</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>37</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>37</v>
@@ -5226,45 +5352,47 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>37</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>48</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>178</v>
+        <v>216</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>37</v>
@@ -5289,13 +5417,13 @@
         <v>37</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>37</v>
+        <v>221</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>37</v>
+        <v>222</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>37</v>
@@ -5313,13 +5441,13 @@
         <v>37</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>60</v>
@@ -5334,13 +5462,13 @@
         <v>37</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>37</v>
@@ -5348,10 +5476,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5371,23 +5499,19 @@
         <v>37</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>238</v>
+        <v>64</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>65</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>37</v>
       </c>
@@ -5435,7 +5559,7 @@
         <v>37</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>67</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>35</v>
@@ -5444,10 +5568,10 @@
         <v>48</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>37</v>
@@ -5456,10 +5580,10 @@
         <v>37</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>245</v>
+        <v>68</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>37</v>
@@ -5470,21 +5594,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>37</v>
@@ -5493,23 +5617,21 @@
         <v>37</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>71</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>248</v>
+        <v>72</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>249</v>
+        <v>73</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>37</v>
       </c>
@@ -5545,31 +5667,31 @@
         <v>37</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>78</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>37</v>
@@ -5578,10 +5700,10 @@
         <v>37</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>253</v>
+        <v>37</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>254</v>
+        <v>62</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>37</v>
@@ -5592,21 +5714,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>256</v>
+        <v>37</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>48</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>49</v>
@@ -5618,19 +5740,19 @@
         <v>49</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>37</v>
@@ -5655,13 +5777,13 @@
         <v>37</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>262</v>
+        <v>37</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>263</v>
+        <v>37</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>37</v>
@@ -5679,13 +5801,13 @@
         <v>37</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>60</v>
@@ -5694,30 +5816,30 @@
         <v>61</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>264</v>
+        <v>37</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>265</v>
+        <v>37</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>268</v>
+        <v>37</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>269</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5740,13 +5862,13 @@
         <v>37</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>180</v>
+        <v>66</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5797,7 +5919,7 @@
         <v>37</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>35</v>
@@ -5821,7 +5943,7 @@
         <v>37</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>37</v>
@@ -5832,14 +5954,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5858,16 +5980,16 @@
         <v>37</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>184</v>
+        <v>73</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5905,19 +6027,19 @@
         <v>37</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>35</v>
@@ -5929,7 +6051,7 @@
         <v>60</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>37</v>
@@ -5952,10 +6074,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5963,13 +6085,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>37</v>
@@ -5978,26 +6100,26 @@
         <v>49</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>188</v>
+        <v>92</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>37</v>
+        <v>252</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>37</v>
@@ -6027,23 +6149,25 @@
         <v>37</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>60</v>
@@ -6058,10 +6182,10 @@
         <v>37</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>37</v>
@@ -6072,20 +6196,18 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>37</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>48</v>
@@ -6100,20 +6222,18 @@
         <v>49</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>188</v>
+        <v>64</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>37</v>
       </c>
@@ -6161,13 +6281,13 @@
         <v>37</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>60</v>
@@ -6182,10 +6302,10 @@
         <v>37</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>37</v>
@@ -6196,10 +6316,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6207,37 +6327,41 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>48</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>179</v>
+        <v>266</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>37</v>
+        <v>270</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>37</v>
@@ -6279,7 +6403,7 @@
         <v>37</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>35</v>
@@ -6288,10 +6412,10 @@
         <v>48</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>37</v>
@@ -6300,10 +6424,10 @@
         <v>37</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>37</v>
+        <v>272</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>69</v>
+        <v>273</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>37</v>
@@ -6314,21 +6438,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>37</v>
@@ -6337,21 +6461,23 @@
         <v>37</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>97</v>
+        <v>276</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>184</v>
+        <v>277</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>37</v>
       </c>
@@ -6387,31 +6513,31 @@
         <v>37</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>185</v>
+        <v>279</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>37</v>
@@ -6420,10 +6546,10 @@
         <v>37</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>37</v>
+        <v>280</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>62</v>
+        <v>281</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>37</v>
@@ -6434,10 +6560,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6445,7 +6571,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>48</v>
@@ -6460,26 +6586,26 @@
         <v>49</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>64</v>
+        <v>284</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>202</v>
+        <v>285</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>203</v>
+        <v>286</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>204</v>
+        <v>287</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>205</v>
+        <v>288</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>282</v>
+        <v>37</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>37</v>
@@ -6521,7 +6647,7 @@
         <v>37</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>207</v>
+        <v>289</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>35</v>
@@ -6542,10 +6668,10 @@
         <v>37</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>208</v>
+        <v>290</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>209</v>
+        <v>291</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>37</v>
@@ -6556,10 +6682,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6582,18 +6708,20 @@
         <v>49</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>212</v>
+        <v>294</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>213</v>
+        <v>295</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>37</v>
       </c>
@@ -6641,7 +6769,7 @@
         <v>37</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>215</v>
+        <v>298</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>35</v>
@@ -6662,10 +6790,10 @@
         <v>37</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>216</v>
+        <v>299</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>217</v>
+        <v>300</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>37</v>
@@ -6676,14 +6804,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>37</v>
+        <v>302</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6693,7 +6821,7 @@
         <v>48</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>37</v>
@@ -6702,26 +6830,26 @@
         <v>49</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>71</v>
+        <v>216</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>220</v>
+        <v>303</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>221</v>
+        <v>304</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>222</v>
+        <v>305</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>223</v>
+        <v>306</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>287</v>
+        <v>37</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>37</v>
@@ -6739,13 +6867,13 @@
         <v>37</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>37</v>
+        <v>307</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>37</v>
+        <v>308</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>37</v>
@@ -6763,10 +6891,10 @@
         <v>37</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>48</v>
@@ -6778,30 +6906,30 @@
         <v>61</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>37</v>
+        <v>309</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>37</v>
+        <v>310</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>226</v>
+        <v>311</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>37</v>
+        <v>313</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>37</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6821,23 +6949,19 @@
         <v>37</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>37</v>
       </c>
@@ -6885,7 +7009,7 @@
         <v>37</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>233</v>
+        <v>67</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>35</v>
@@ -6894,10 +7018,10 @@
         <v>48</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>37</v>
@@ -6906,10 +7030,10 @@
         <v>37</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>234</v>
+        <v>37</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>37</v>
@@ -6920,21 +7044,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>37</v>
@@ -6943,23 +7067,21 @@
         <v>37</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>238</v>
+        <v>71</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>239</v>
+        <v>72</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>37</v>
       </c>
@@ -6995,31 +7117,31 @@
         <v>37</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>37</v>
@@ -7028,10 +7150,10 @@
         <v>37</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>245</v>
+        <v>62</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>37</v>
@@ -7042,10 +7164,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7056,7 +7178,7 @@
         <v>35</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>37</v>
@@ -7068,19 +7190,19 @@
         <v>49</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>37</v>
@@ -7117,25 +7239,23 @@
         <v>37</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>37</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>60</v>
@@ -7150,10 +7270,10 @@
         <v>37</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>37</v>
@@ -7164,12 +7284,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>37</v>
       </c>
@@ -7181,7 +7303,7 @@
         <v>48</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>37</v>
@@ -7190,19 +7312,19 @@
         <v>49</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>294</v>
+        <v>108</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>295</v>
+        <v>235</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>37</v>
@@ -7251,34 +7373,34 @@
         <v>37</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>299</v>
+        <v>37</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>302</v>
+        <v>37</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>37</v>
@@ -7286,10 +7408,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7300,7 +7422,7 @@
         <v>35</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>37</v>
@@ -7309,20 +7431,18 @@
         <v>37</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>304</v>
+        <v>64</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
+        <v>65</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>37</v>
@@ -7371,19 +7491,19 @@
         <v>37</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>303</v>
+        <v>67</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>37</v>
@@ -7392,13 +7512,13 @@
         <v>37</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>266</v>
+        <v>37</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>308</v>
+        <v>68</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>302</v>
+        <v>37</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>37</v>
@@ -7406,21 +7526,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>310</v>
+        <v>70</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>37</v>
@@ -7429,23 +7549,21 @@
         <v>37</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>311</v>
+        <v>71</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>312</v>
+        <v>72</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>313</v>
+        <v>73</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>37</v>
       </c>
@@ -7481,46 +7599,46 @@
         <v>37</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>309</v>
+        <v>78</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>316</v>
+        <v>37</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>317</v>
+        <v>37</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>318</v>
+        <v>62</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>319</v>
+        <v>37</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>37</v>
@@ -7528,14 +7646,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>321</v>
+        <v>37</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7545,7 +7663,7 @@
         <v>48</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>37</v>
@@ -7554,26 +7672,26 @@
         <v>49</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>322</v>
+        <v>92</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>323</v>
+        <v>248</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>324</v>
+        <v>249</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>37</v>
+        <v>327</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>37</v>
@@ -7615,7 +7733,7 @@
         <v>37</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>320</v>
+        <v>253</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>35</v>
@@ -7624,25 +7742,25 @@
         <v>48</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>327</v>
+        <v>60</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>328</v>
+        <v>61</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>329</v>
+        <v>37</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>331</v>
+        <v>255</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>332</v>
+        <v>37</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>37</v>
@@ -7650,10 +7768,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7676,16 +7794,16 @@
         <v>49</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>334</v>
+        <v>64</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>335</v>
+        <v>258</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>336</v>
+        <v>259</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>337</v>
+        <v>260</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7735,7 +7853,7 @@
         <v>37</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>333</v>
+        <v>261</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>35</v>
@@ -7756,13 +7874,13 @@
         <v>37</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>339</v>
+        <v>263</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>340</v>
+        <v>37</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>37</v>
@@ -7770,10 +7888,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7781,10 +7899,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>37</v>
@@ -7796,26 +7914,26 @@
         <v>49</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>343</v>
+        <v>266</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>344</v>
+        <v>267</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>345</v>
+        <v>269</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>37</v>
+        <v>332</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>37</v>
@@ -7857,34 +7975,34 @@
         <v>37</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>341</v>
+        <v>271</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>346</v>
+        <v>37</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>347</v>
+        <v>272</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>348</v>
+        <v>273</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>349</v>
+        <v>37</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>37</v>
@@ -7892,10 +8010,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7909,7 +8027,7 @@
         <v>48</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>37</v>
@@ -7918,19 +8036,19 @@
         <v>49</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>351</v>
+        <v>64</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>352</v>
+        <v>276</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>352</v>
+        <v>277</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>353</v>
+        <v>268</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>354</v>
+        <v>278</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>37</v>
@@ -7967,17 +8085,19 @@
         <v>37</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>356</v>
+        <v>37</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>350</v>
+        <v>279</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>35</v>
@@ -7986,7 +8106,7 @@
         <v>48</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>357</v>
+        <v>60</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>61</v>
@@ -7995,31 +8115,29 @@
         <v>37</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>358</v>
+        <v>37</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>359</v>
+        <v>280</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>360</v>
+        <v>281</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>361</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>37</v>
       </c>
@@ -8031,7 +8149,7 @@
         <v>48</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>37</v>
@@ -8040,19 +8158,19 @@
         <v>49</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>364</v>
+        <v>284</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
+        <v>285</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>352</v>
+        <v>286</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>353</v>
+        <v>287</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>354</v>
+        <v>288</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>37</v>
@@ -8101,7 +8219,7 @@
         <v>37</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>350</v>
+        <v>289</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>35</v>
@@ -8110,7 +8228,7 @@
         <v>48</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>357</v>
+        <v>60</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>61</v>
@@ -8119,27 +8237,27 @@
         <v>37</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>358</v>
+        <v>37</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>360</v>
+        <v>291</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>361</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8159,19 +8277,23 @@
         <v>37</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>179</v>
+        <v>294</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>37</v>
       </c>
@@ -8219,7 +8341,7 @@
         <v>37</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>181</v>
+        <v>298</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>35</v>
@@ -8228,10 +8350,10 @@
         <v>48</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>37</v>
@@ -8240,10 +8362,10 @@
         <v>37</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>37</v>
+        <v>299</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>69</v>
+        <v>300</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>37</v>
@@ -8254,44 +8376,46 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>96</v>
+        <v>339</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>97</v>
+        <v>340</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>184</v>
+        <v>341</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>37</v>
       </c>
@@ -8327,46 +8451,46 @@
         <v>37</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>185</v>
+        <v>338</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>37</v>
+        <v>344</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>37</v>
+        <v>345</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>62</v>
+        <v>346</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>37</v>
@@ -8374,10 +8498,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8385,13 +8509,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>37</v>
@@ -8400,20 +8524,18 @@
         <v>49</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>37</v>
       </c>
@@ -8461,19 +8583,19 @@
         <v>37</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>37</v>
@@ -8482,13 +8604,13 @@
         <v>37</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>377</v>
+        <v>311</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>37</v>
@@ -8496,14 +8618,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>37</v>
+        <v>355</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8516,32 +8638,30 @@
         <v>37</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>49</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>71</v>
+        <v>356</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>222</v>
+        <v>359</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="Q53" t="s" s="2">
-        <v>384</v>
-      </c>
+      <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
         <v>37</v>
       </c>
@@ -8561,13 +8681,13 @@
         <v>37</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>386</v>
+        <v>37</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>37</v>
@@ -8585,7 +8705,7 @@
         <v>37</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>387</v>
+        <v>354</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>35</v>
@@ -8597,22 +8717,22 @@
         <v>60</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>37</v>
+        <v>361</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>37</v>
+        <v>364</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>37</v>
@@ -8620,14 +8740,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>37</v>
+        <v>366</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8646,19 +8766,19 @@
         <v>49</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>222</v>
+        <v>370</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>37</v>
@@ -8707,7 +8827,7 @@
         <v>37</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>35</v>
@@ -8716,25 +8836,25 @@
         <v>48</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>60</v>
+        <v>372</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>61</v>
+        <v>373</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>37</v>
+        <v>374</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>37</v>
+        <v>377</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>37</v>
@@ -8742,10 +8862,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8753,13 +8873,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>48</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>37</v>
@@ -8768,26 +8888,24 @@
         <v>49</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>404</v>
+        <v>37</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>37</v>
@@ -8829,7 +8947,7 @@
         <v>37</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>378</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>35</v>
@@ -8838,7 +8956,7 @@
         <v>48</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>406</v>
+        <v>60</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>61</v>
@@ -8850,13 +8968,13 @@
         <v>37</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>37</v>
+        <v>384</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>37</v>
@@ -8864,10 +8982,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8875,13 +8993,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>37</v>
@@ -8890,19 +9008,19 @@
         <v>49</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>71</v>
+        <v>386</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>411</v>
+        <v>187</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>37</v>
@@ -8927,13 +9045,13 @@
         <v>37</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>413</v>
+        <v>37</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>414</v>
+        <v>37</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>37</v>
@@ -8951,34 +9069,34 @@
         <v>37</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>37</v>
+        <v>390</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>37</v>
+        <v>393</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>37</v>
@@ -8986,10 +9104,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9009,22 +9127,22 @@
         <v>37</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>163</v>
+        <v>395</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>419</v>
+        <v>396</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>37</v>
@@ -9049,31 +9167,29 @@
         <v>37</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>422</v>
+        <v>37</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>423</v>
+        <v>37</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>37</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>37</v>
+        <v>400</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>35</v>
@@ -9082,7 +9198,7 @@
         <v>48</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>61</v>
@@ -9091,62 +9207,64 @@
         <v>37</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>37</v>
+        <v>402</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>62</v>
+        <v>403</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>37</v>
+        <v>405</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="D58" t="s" s="2">
-        <v>427</v>
+        <v>37</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>163</v>
+        <v>408</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>428</v>
+        <v>396</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>429</v>
+        <v>396</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>37</v>
@@ -9171,13 +9289,13 @@
         <v>37</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>432</v>
+        <v>37</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>433</v>
+        <v>37</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>37</v>
@@ -9195,16 +9313,16 @@
         <v>37</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>60</v>
+        <v>401</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>61</v>
@@ -9213,27 +9331,27 @@
         <v>37</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>435</v>
+        <v>403</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>437</v>
+        <v>405</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>438</v>
+        <v>409</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9244,7 +9362,7 @@
         <v>35</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>37</v>
@@ -9256,20 +9374,16 @@
         <v>37</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>439</v>
+        <v>64</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>440</v>
+        <v>65</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>37</v>
       </c>
@@ -9317,19 +9431,19 @@
         <v>37</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>438</v>
+        <v>67</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>37</v>
@@ -9338,10 +9452,10 @@
         <v>37</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>444</v>
+        <v>37</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>445</v>
+        <v>68</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>37</v>
@@ -9352,21 +9466,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>446</v>
+        <v>412</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>37</v>
@@ -9378,16 +9492,16 @@
         <v>37</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>447</v>
+        <v>72</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>448</v>
+        <v>73</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>449</v>
+        <v>74</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9413,69 +9527,69 @@
         <v>37</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>450</v>
+        <v>37</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>451</v>
+        <v>37</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>452</v>
+        <v>37</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>453</v>
+        <v>37</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>454</v>
+        <v>37</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>455</v>
+        <v>62</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>456</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>457</v>
+        <v>413</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9483,34 +9597,34 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>48</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>163</v>
+        <v>415</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>458</v>
+        <v>416</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>459</v>
+        <v>417</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>460</v>
+        <v>418</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>461</v>
+        <v>419</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>37</v>
@@ -9535,11 +9649,13 @@
         <v>37</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>462</v>
+        <v>37</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>37</v>
@@ -9557,7 +9673,7 @@
         <v>37</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>457</v>
+        <v>420</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>35</v>
@@ -9578,10 +9694,10 @@
         <v>37</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>463</v>
+        <v>421</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>37</v>
@@ -9592,10 +9708,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>465</v>
+        <v>424</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9612,28 +9728,32 @@
         <v>37</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>466</v>
+        <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>467</v>
+        <v>425</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="Q62" s="2"/>
+      <c r="Q62" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="R62" t="s" s="2">
         <v>37</v>
       </c>
@@ -9653,13 +9773,13 @@
         <v>37</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>37</v>
+        <v>429</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>37</v>
+        <v>430</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>37</v>
@@ -9677,7 +9797,7 @@
         <v>37</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>465</v>
+        <v>431</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>35</v>
@@ -9689,33 +9809,33 @@
         <v>60</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>470</v>
+        <v>37</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>471</v>
+        <v>432</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>472</v>
+        <v>433</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>473</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>474</v>
+        <v>434</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>474</v>
+        <v>435</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9723,33 +9843,35 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>48</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>475</v>
+        <v>64</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>476</v>
+        <v>436</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>477</v>
+        <v>437</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>37</v>
       </c>
@@ -9797,7 +9919,7 @@
         <v>37</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>474</v>
+        <v>439</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>35</v>
@@ -9809,33 +9931,33 @@
         <v>60</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>479</v>
+        <v>37</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>481</v>
+        <v>441</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>482</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>442</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>483</v>
+        <v>443</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9843,41 +9965,41 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>484</v>
+        <v>92</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>486</v>
+        <v>445</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>487</v>
+        <v>446</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>488</v>
+        <v>447</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>37</v>
+        <v>448</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>37</v>
@@ -9919,19 +10041,19 @@
         <v>37</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>483</v>
+        <v>449</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>489</v>
+        <v>61</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>37</v>
@@ -9940,10 +10062,10 @@
         <v>37</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>491</v>
+        <v>451</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>37</v>
@@ -9954,10 +10076,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>452</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>453</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9965,31 +10087,35 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>48</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>179</v>
+        <v>454</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>37</v>
       </c>
@@ -10013,13 +10139,13 @@
         <v>37</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>37</v>
+        <v>457</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>37</v>
+        <v>458</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>37</v>
@@ -10037,7 +10163,7 @@
         <v>37</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>181</v>
+        <v>459</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>35</v>
@@ -10046,10 +10172,10 @@
         <v>48</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>37</v>
@@ -10058,10 +10184,10 @@
         <v>37</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>37</v>
+        <v>440</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>69</v>
+        <v>460</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>37</v>
@@ -10072,24 +10198,24 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>37</v>
@@ -10098,18 +10224,20 @@
         <v>37</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>96</v>
+        <v>216</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>97</v>
+        <v>462</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>184</v>
+        <v>463</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>37</v>
       </c>
@@ -10133,43 +10261,43 @@
         <v>37</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>37</v>
+        <v>466</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>37</v>
+        <v>467</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>185</v>
+        <v>461</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>60</v>
+        <v>468</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>37</v>
@@ -10178,10 +10306,10 @@
         <v>37</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>62</v>
+        <v>469</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>37</v>
@@ -10192,14 +10320,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10212,25 +10340,25 @@
         <v>37</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>96</v>
+        <v>216</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>99</v>
+        <v>474</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>118</v>
+        <v>475</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>37</v>
@@ -10255,13 +10383,13 @@
         <v>37</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>37</v>
+        <v>476</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>37</v>
+        <v>477</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>37</v>
@@ -10279,7 +10407,7 @@
         <v>37</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>35</v>
@@ -10291,33 +10419,33 @@
         <v>60</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>37</v>
+        <v>478</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>37</v>
+        <v>479</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>62</v>
+        <v>480</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>37</v>
+        <v>481</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10328,7 +10456,7 @@
         <v>35</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>37</v>
@@ -10340,18 +10468,20 @@
         <v>37</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>37</v>
       </c>
@@ -10399,19 +10529,19 @@
         <v>37</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>504</v>
+        <v>60</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>505</v>
+        <v>61</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>37</v>
@@ -10420,10 +10550,10 @@
         <v>37</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>37</v>
@@ -10434,10 +10564,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10460,16 +10590,16 @@
         <v>37</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>500</v>
+        <v>216</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10495,13 +10625,13 @@
         <v>37</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>37</v>
+        <v>494</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>37</v>
+        <v>495</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>37</v>
@@ -10519,7 +10649,7 @@
         <v>37</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>35</v>
@@ -10528,36 +10658,36 @@
         <v>48</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>504</v>
+        <v>60</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>505</v>
+        <v>61</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>37</v>
+        <v>496</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>37</v>
+        <v>499</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10580,19 +10710,19 @@
         <v>37</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>37</v>
@@ -10617,13 +10747,11 @@
         <v>37</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>37</v>
@@ -10641,7 +10769,7 @@
         <v>37</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>35</v>
@@ -10659,13 +10787,13 @@
         <v>37</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>519</v>
+        <v>37</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>436</v>
+        <v>507</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>37</v>
@@ -10676,10 +10804,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10690,7 +10818,7 @@
         <v>35</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>37</v>
@@ -10702,20 +10830,18 @@
         <v>37</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>163</v>
+        <v>509</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>525</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>37</v>
       </c>
@@ -10739,13 +10865,13 @@
         <v>37</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>450</v>
+        <v>37</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>526</v>
+        <v>37</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>527</v>
+        <v>37</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>37</v>
@@ -10763,45 +10889,45 @@
         <v>37</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>436</v>
+        <v>515</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>37</v>
+        <v>516</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10824,20 +10950,18 @@
         <v>37</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>37</v>
       </c>
@@ -10885,7 +11009,7 @@
         <v>37</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>35</v>
@@ -10897,33 +11021,33 @@
         <v>60</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>534</v>
+        <v>189</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>37</v>
+        <v>522</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>37</v>
+        <v>525</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10934,7 +11058,7 @@
         <v>35</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>37</v>
@@ -10946,18 +11070,20 @@
         <v>37</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>178</v>
+        <v>527</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>37</v>
       </c>
@@ -11005,19 +11131,19 @@
         <v>37</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>61</v>
+        <v>532</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>37</v>
@@ -11026,10 +11152,10 @@
         <v>37</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>506</v>
+        <v>533</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>37</v>
@@ -11040,10 +11166,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11054,7 +11180,7 @@
         <v>35</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>37</v>
@@ -11063,20 +11189,18 @@
         <v>37</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>542</v>
+        <v>64</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>543</v>
+        <v>65</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>37</v>
@@ -11125,19 +11249,19 @@
         <v>37</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>541</v>
+        <v>67</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>37</v>
@@ -11146,10 +11270,10 @@
         <v>37</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>546</v>
+        <v>37</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>547</v>
+        <v>68</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>37</v>
@@ -11160,14 +11284,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11183,19 +11307,19 @@
         <v>37</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>549</v>
+        <v>71</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>550</v>
+        <v>72</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>551</v>
+        <v>73</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>552</v>
+        <v>74</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11233,19 +11357,19 @@
         <v>37</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>35</v>
@@ -11257,7 +11381,7 @@
         <v>60</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>37</v>
@@ -11266,10 +11390,10 @@
         <v>37</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>546</v>
+        <v>37</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>553</v>
+        <v>62</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>37</v>
@@ -11280,14 +11404,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>37</v>
+        <v>538</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11297,28 +11421,28 @@
         <v>36</v>
       </c>
       <c r="H76" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I76" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>37</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>49</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>484</v>
+        <v>71</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>556</v>
+        <v>74</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>557</v>
+        <v>171</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>37</v>
@@ -11367,7 +11491,7 @@
         <v>37</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>35</v>
@@ -11379,7 +11503,7 @@
         <v>60</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>558</v>
+        <v>79</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>37</v>
@@ -11388,10 +11512,10 @@
         <v>37</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>559</v>
+        <v>37</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>560</v>
+        <v>62</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>37</v>
@@ -11402,10 +11526,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11428,15 +11552,17 @@
         <v>37</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>178</v>
+        <v>543</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>179</v>
+        <v>544</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>37</v>
@@ -11485,7 +11611,7 @@
         <v>37</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>181</v>
+        <v>542</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>35</v>
@@ -11494,10 +11620,10 @@
         <v>48</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>37</v>
+        <v>547</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>37</v>
+        <v>548</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>37</v>
@@ -11506,10 +11632,10 @@
         <v>37</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>37</v>
+        <v>549</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>69</v>
+        <v>550</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>37</v>
@@ -11520,21 +11646,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>37</v>
@@ -11546,16 +11672,16 @@
         <v>37</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>96</v>
+        <v>543</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>97</v>
+        <v>552</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>184</v>
+        <v>553</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>99</v>
+        <v>546</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11593,31 +11719,31 @@
         <v>37</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>185</v>
+        <v>551</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>60</v>
+        <v>547</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>104</v>
+        <v>548</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>37</v>
@@ -11626,10 +11752,10 @@
         <v>37</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>37</v>
+        <v>549</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>62</v>
+        <v>554</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>37</v>
@@ -11640,45 +11766,45 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>495</v>
+        <v>37</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>37</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>96</v>
+        <v>216</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>496</v>
+        <v>556</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>497</v>
+        <v>557</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>99</v>
+        <v>558</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>118</v>
+        <v>559</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>37</v>
@@ -11703,13 +11829,13 @@
         <v>37</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>37</v>
+        <v>560</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>37</v>
+        <v>561</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>37</v>
@@ -11727,31 +11853,31 @@
         <v>37</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>498</v>
+        <v>555</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>60</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>37</v>
+        <v>562</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>37</v>
+        <v>563</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>62</v>
+        <v>480</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>37</v>
@@ -11773,22 +11899,22 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>565</v>
@@ -11825,13 +11951,13 @@
         <v>37</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>261</v>
+        <v>122</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>262</v>
+        <v>569</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>263</v>
+        <v>570</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>37</v>
@@ -11852,10 +11978,10 @@
         <v>564</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>60</v>
@@ -11867,16 +11993,16 @@
         <v>37</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>266</v>
+        <v>563</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>267</v>
+        <v>480</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>268</v>
+        <v>37</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>37</v>
@@ -11884,10 +12010,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11901,28 +12027,28 @@
         <v>48</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>37</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>351</v>
+        <v>572</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>354</v>
+        <v>576</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>37</v>
@@ -11947,13 +12073,13 @@
         <v>37</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>574</v>
+        <v>37</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>575</v>
+        <v>37</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>37</v>
@@ -11971,7 +12097,7 @@
         <v>37</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>35</v>
@@ -11980,36 +12106,36 @@
         <v>48</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>576</v>
+        <v>60</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>61</v>
+        <v>577</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>577</v>
+        <v>37</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>359</v>
+        <v>578</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>360</v>
+        <v>579</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>361</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12023,7 +12149,7 @@
         <v>48</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>37</v>
@@ -12032,20 +12158,18 @@
         <v>37</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>163</v>
+        <v>64</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>37</v>
       </c>
@@ -12069,13 +12193,13 @@
         <v>37</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>422</v>
+        <v>37</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>423</v>
+        <v>37</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>37</v>
@@ -12093,7 +12217,7 @@
         <v>37</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>35</v>
@@ -12102,7 +12226,7 @@
         <v>48</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>582</v>
+        <v>60</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>61</v>
@@ -12114,10 +12238,10 @@
         <v>37</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>62</v>
+        <v>549</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>425</v>
+        <v>583</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>37</v>
@@ -12128,14 +12252,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>427</v>
+        <v>37</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12151,23 +12275,21 @@
         <v>37</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>163</v>
+        <v>585</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>428</v>
+        <v>586</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>429</v>
+        <v>587</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>37</v>
       </c>
@@ -12191,13 +12313,13 @@
         <v>37</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>432</v>
+        <v>37</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>433</v>
+        <v>37</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>37</v>
@@ -12215,7 +12337,7 @@
         <v>37</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>35</v>
@@ -12227,33 +12349,33 @@
         <v>60</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>434</v>
+        <v>37</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>435</v>
+        <v>589</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>436</v>
+        <v>590</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>437</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12273,23 +12395,21 @@
         <v>37</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>38</v>
+        <v>592</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>37</v>
       </c>
@@ -12337,7 +12457,7 @@
         <v>37</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>35</v>
@@ -12346,10 +12466,10 @@
         <v>36</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>37</v>
@@ -12358,20 +12478,1112 @@
         <v>37</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>490</v>
+        <v>589</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>491</v>
+        <v>596</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AP84" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP84">
+  <autoFilter ref="A1:AP93">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12381,7 +13593,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI92">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
